--- a/samples/converted/02_scanned_inventory.xlsx
+++ b/samples/converted/02_scanned_inventory.xlsx
@@ -12,9 +12,11 @@
     <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Corrections" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Page coverage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Run log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Overview'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Table 1'!$A$1:$P$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Table 1'!$1:$1</definedName>
@@ -24,6 +26,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Evidence'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Corrections'!$A$1:$F$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Corrections'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Page coverage'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Page coverage'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Run log'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Run log'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -85,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -99,6 +105,9 @@
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -106,6 +115,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -504,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -592,7 +604,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>24.02</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -615,36 +627,106 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LedgerLens 1.0 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
+          <t>LedgerLens 1.1 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Interpretation</t>
+          <t>Review status</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OCR recognition scores are not measured extraction accuracy. Review all findings.</t>
+          <t>Draft — review pending</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Pages with extracted tables</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2 / 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Validation errors</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Validation warnings</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rows with source evidence</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Review note</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Review completed (UTC)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>OCR recognition scores are not measured extraction accuracy. Review all findings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Pages without extracted tables are explicitly flagged. No guarantee for arbitrary layouts.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -781,19 +863,19 @@
       <c r="E2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="6" t="n">
         <v>52.8</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -827,7 +909,7 @@
           <t>SKU-0002</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -840,22 +922,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="10" t="n">
         <v>74.8</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -905,19 +987,19 @@
       <c r="E4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="6" t="n">
         <v>99</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -951,7 +1033,7 @@
           <t>SKU-0004</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>46299</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -964,22 +1046,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="10" t="n">
         <v>114</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="10" t="n">
         <v>11.4</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="10" t="n">
         <v>125.4</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1029,19 +1111,19 @@
       <c r="E6" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>154</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1075,7 +1157,7 @@
           <t>SKU-0006</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1088,22 +1170,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="10" t="n">
         <v>168</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="10" t="n">
         <v>184.8</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1153,19 +1235,19 @@
       <c r="E8" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="6" t="n">
         <v>198</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="6" t="n">
         <v>217.8</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1199,7 +1281,7 @@
           <t>SKU-0008</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1212,22 +1294,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="10" t="n">
         <v>230</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="J9" s="10" t="n">
         <v>253</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1277,19 +1359,19 @@
       <c r="E10" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="6" t="n">
         <v>264</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="6" t="n">
         <v>26.4</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="6" t="n">
         <v>290.4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1323,7 +1405,7 @@
           <t>SKU-0010</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <v>46305</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1336,22 +1418,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="J11" s="10" t="n">
         <v>330</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1401,19 +1483,19 @@
       <c r="E12" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="6" t="n">
         <v>338</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="6" t="n">
         <v>33.8</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="6" t="n">
         <v>371.8</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1447,7 +1529,7 @@
           <t>SKU-0012</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1460,22 +1542,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="10" t="n">
         <v>378</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="10" t="n">
         <v>37.8</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="10" t="n">
         <v>415.8</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1525,19 +1607,19 @@
       <c r="E14" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="6" t="n">
         <v>420</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J14" s="6" t="n">
         <v>462</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1571,7 +1653,7 @@
           <t>SKU-0014</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1584,22 +1666,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="10" t="n">
         <v>464</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="10" t="n">
         <v>46.4</v>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="J15" s="10" t="n">
         <v>510.4</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1649,19 +1731,19 @@
       <c r="E16" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J16" s="6" t="n">
         <v>561</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1695,7 +1777,7 @@
           <t>SKU-0016</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1708,22 +1790,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="10" t="n">
         <v>558</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="10" t="n">
         <v>55.8</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="J17" s="10" t="n">
         <v>613.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -1773,19 +1855,19 @@
       <c r="E18" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="6" t="n">
         <v>608</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I18" s="6" t="n">
         <v>60.8</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J18" s="6" t="n">
         <v>668.8</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1819,7 +1901,7 @@
           <t>SKU-0018</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="8" t="n">
         <v>46313</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1832,22 +1914,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="10" t="n">
         <v>660</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="J19" s="8" t="n">
+      <c r="J19" s="10" t="n">
         <v>726</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -1897,19 +1979,19 @@
       <c r="E20" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H20" s="6" t="n">
         <v>714</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I20" s="6" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J20" s="6" t="n">
         <v>785.4</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1943,7 +2025,7 @@
           <t>SKU-0020</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="8" t="n">
         <v>46315</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1956,22 +2038,22 @@
           <t>Depot A</t>
         </is>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="10" t="n">
         <v>770</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="J21" s="8" t="n">
+      <c r="J21" s="10" t="n">
         <v>847</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -2675,4 +2757,360 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Extraction</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Table fragments</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Data rows (page estimate)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Attempts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Time (UTC)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:37.562230+00:00</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>inspect</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Opened source document</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:37.564626+00:00</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>inspect</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Selected OCR extraction</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:37.564626+00:00</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Running local OCR and layout reconstruction</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:45.755686+00:00</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Extracted table fragments</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:45.755686+00:00</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>inspect</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Selected OCR extraction</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:45.755686+00:00</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Running local OCR and layout reconstruction</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.371613+00:00</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Extracted table fragments</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.372615+00:00</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>align</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Matching table schemas and continuation pages</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.374615+00:00</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>validate</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Checking totals, arithmetic, balances and table integrity</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.377615+00:00</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Extraction complete; human review is pending</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/samples/converted/02_scanned_inventory.xlsx
+++ b/samples/converted/02_scanned_inventory.xlsx
@@ -526,7 +526,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LedgerLens extraction report</t>
+          <t>DamnLens AI Agent extraction report</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>13.82</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -615,7 +615,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>18b987c304b7f20ddd13b37c0f4051d74203c9510bde61e8a9e425955feb4d41</t>
+          <t>ca2b466e8dc8a87bbff3dbaafe7d26f8416393eab1e7d36931a279b6d93d031a</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LedgerLens 1.1 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
+          <t>DamnLens AI Agent 1.2 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.998</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.998</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -2830,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8.19</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5.61</v>
+        <v>6.72</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:37.562230+00:00</t>
+          <t>2026-10-15T06:39:50.490151+00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:37.564626+00:00</t>
+          <t>2026-10-15T06:39:50.500905+00:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2957,7 +2957,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:37.564626+00:00</t>
+          <t>2026-10-15T06:39:50.500905+00:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:45.755686+00:00</t>
+          <t>2026-10-15T06:39:59.533759+00:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2997,7 +2997,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:45.755686+00:00</t>
+          <t>2026-10-15T06:39:59.543723+00:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:45.755686+00:00</t>
+          <t>2026-10-15T06:39:59.543723+00:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.371613+00:00</t>
+          <t>2026-10-15T06:40:06.265665+00:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.372615+00:00</t>
+          <t>2026-10-15T06:40:06.265665+00:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3075,7 +3075,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.374615+00:00</t>
+          <t>2026-10-15T06:40:06.267247+00:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.377615+00:00</t>
+          <t>2026-10-15T06:40:06.270583+00:00</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">

--- a/samples/converted/02_scanned_inventory.xlsx
+++ b/samples/converted/02_scanned_inventory.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>15.78</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -627,7 +627,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>DamnLens AI Agent 1.2 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
+          <t>DamnLens AI Agent 1.3 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9.039999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6.72</v>
+        <v>6.39</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:39:50.490151+00:00</t>
+          <t>2026-10-15T07:48:14.413926+00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:39:50.500905+00:00</t>
+          <t>2026-10-15T07:48:14.416160+00:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2957,7 +2957,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:39:50.500905+00:00</t>
+          <t>2026-10-15T07:48:14.416160+00:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:39:59.533759+00:00</t>
+          <t>2026-10-15T07:48:22.744569+00:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2997,7 +2997,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:39:59.543723+00:00</t>
+          <t>2026-10-15T07:48:22.745551+00:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:39:59.543723+00:00</t>
+          <t>2026-10-15T07:48:22.745551+00:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.265665+00:00</t>
+          <t>2026-10-15T07:48:29.130771+00:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.265665+00:00</t>
+          <t>2026-10-15T07:48:29.131563+00:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3075,7 +3075,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.267247+00:00</t>
+          <t>2026-10-15T07:48:29.134203+00:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.270583+00:00</t>
+          <t>2026-10-15T07:48:29.136206+00:00</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">

--- a/samples/converted/02_scanned_inventory.xlsx
+++ b/samples/converted/02_scanned_inventory.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>14.73</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -627,7 +627,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>DamnLens AI Agent 1.3 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
+          <t>DamnLens AI Agent 1.4 · PyMuPDF + RapidOCR (PP-OCRv3/v5 / ONNX)</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 174.76, 994.58, 202.91]</t>
+          <t>[43.85, 174.76, 994.42, 202.75]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 202.91, 994.58, 230.73]</t>
+          <t>[43.85, 202.75, 994.42, 230.73]</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 230.73, 994.58, 258.71]</t>
+          <t>[43.85, 230.73, 994.42, 258.71]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 258.71, 994.58, 286.69]</t>
+          <t>[43.85, 258.71, 994.42, 286.69]</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 286.69, 994.58, 314.67]</t>
+          <t>[43.85, 286.69, 994.42, 314.67]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 314.67, 994.58, 342.65]</t>
+          <t>[43.85, 314.67, 994.42, 342.65]</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 342.65, 994.58, 370.8]</t>
+          <t>[43.85, 342.65, 994.42, 370.64]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 370.8, 994.58, 398.62]</t>
+          <t>[43.85, 370.64, 994.42, 398.62]</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 398.62, 994.58, 426.6]</t>
+          <t>[43.85, 398.62, 994.42, 426.76]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 426.6, 994.58, 454.58]</t>
+          <t>[43.85, 426.76, 994.42, 454.75]</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 174.76, 994.58, 202.91]</t>
+          <t>[43.85, 174.76, 994.42, 202.75]</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 202.91, 994.58, 230.73]</t>
+          <t>[43.85, 202.75, 994.42, 230.73]</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 230.73, 994.58, 258.71]</t>
+          <t>[43.85, 230.73, 994.42, 258.71]</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 258.71, 994.58, 286.69]</t>
+          <t>[43.85, 258.71, 994.42, 286.69]</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 286.69, 994.58, 314.67]</t>
+          <t>[43.85, 286.69, 994.42, 314.67]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 314.67, 994.58, 342.65]</t>
+          <t>[43.85, 314.67, 994.42, 342.65]</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 342.65, 994.58, 370.8]</t>
+          <t>[43.85, 342.65, 994.42, 370.64]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 370.8, 994.58, 398.62]</t>
+          <t>[43.85, 370.64, 994.42, 398.62]</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>[43.85, 398.62, 994.58, 426.6]</t>
+          <t>[43.85, 398.62, 994.42, 426.76]</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>[43.85, 426.6, 994.58, 454.58]</t>
+          <t>[43.85, 426.76, 994.42, 454.75]</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2830,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8.34</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6.39</v>
+        <v>6.69</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:14.413926+00:00</t>
+          <t>2026-10-15T08:42:19.057941+00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:14.416160+00:00</t>
+          <t>2026-10-15T08:42:19.059720+00:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2957,7 +2957,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:14.416160+00:00</t>
+          <t>2026-10-15T08:42:19.059720+00:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:22.744569+00:00</t>
+          <t>2026-10-15T08:42:27.599816+00:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2997,7 +2997,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:22.745551+00:00</t>
+          <t>2026-10-15T08:42:27.601819+00:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:22.745551+00:00</t>
+          <t>2026-10-15T08:42:27.601819+00:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.130771+00:00</t>
+          <t>2026-10-15T08:42:34.283842+00:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.131563+00:00</t>
+          <t>2026-10-15T08:42:34.283842+00:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3075,7 +3075,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.134203+00:00</t>
+          <t>2026-10-15T08:42:34.283842+00:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.136206+00:00</t>
+          <t>2026-10-15T08:42:34.294107+00:00</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">

--- a/samples/converted/02_scanned_inventory.xlsx
+++ b/samples/converted/02_scanned_inventory.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Run log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Overview'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Table 1'!$A$1:$P$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Table 1'!$1:$1</definedName>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>15.24</v>
+        <v>13.71</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -634,31 +634,31 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Review status</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Draft — review pending</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Pages with extracted tables</t>
+          <t>Gemini model</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2 / 2</t>
+          <t>Not used</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Validation errors</t>
+          <t>Gemini request attempts</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -668,7 +668,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Validation warnings</t>
+          <t>Gemini reported total tokens</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -678,55 +678,111 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Rows with source evidence</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>20</v>
+          <t>Gemini interpretation</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>No external AI API requests.</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Review note</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
+          <t>Review status</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Draft — review pending</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Review completed (UTC)</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr"/>
+          <t>Pages with extracted tables</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2 / 2</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>OCR recognition scores are not measured extraction accuracy. Review all findings.</t>
-        </is>
+          <t>Validation errors</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Validation warnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Rows with source evidence</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Review note</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Review completed (UTC)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>OCR recognition scores are not measured extraction accuracy. Review all findings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Pages without extracted tables are explicitly flagged. No guarantee for arbitrary layouts.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B19"/>
+  <autoFilter ref="A1:B24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2830,7 +2886,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2915,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6.69</v>
+        <v>6.05</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2919,7 +2975,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:19.057941+00:00</t>
+          <t>2026-10-15T09:24:51.814817+00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2937,7 +2993,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:19.059720+00:00</t>
+          <t>2026-10-15T09:24:51.818135+00:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2957,7 +3013,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:19.059720+00:00</t>
+          <t>2026-10-15T09:24:51.818135+00:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2977,7 +3033,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:27.599816+00:00</t>
+          <t>2026-10-15T09:24:59.468029+00:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2997,7 +3053,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:27.601819+00:00</t>
+          <t>2026-10-15T09:24:59.470034+00:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3017,7 +3073,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:27.601819+00:00</t>
+          <t>2026-10-15T09:24:59.470034+00:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3037,7 +3093,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.283842+00:00</t>
+          <t>2026-10-15T09:25:05.516151+00:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3057,7 +3113,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.283842+00:00</t>
+          <t>2026-10-15T09:25:05.516151+00:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3075,7 +3131,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.283842+00:00</t>
+          <t>2026-10-15T09:25:05.519626+00:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3093,7 +3149,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.294107+00:00</t>
+          <t>2026-10-15T09:25:05.522900+00:00</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
